--- a/html/Socialfaglige systemer_excel.XLSX
+++ b/html/Socialfaglige systemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F939288B-4510-44DE-94BC-0DD62A808CE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5206210E-0928-45E4-A766-688B10649659}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30855" yWindow="1950" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 19-12-2025" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 29-01-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Socialfaglige_systemer">'Opdateret d. 19-12-2025'!$A$1:$E$11</definedName>
+    <definedName name="Socialfaglige_systemer">'Opdateret d. 29-01-2026'!$A$1:$E$11</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Socialfaglige systemer_excel.XLSX
+++ b/html/Socialfaglige systemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5206210E-0928-45E4-A766-688B10649659}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9673C411-FA17-460A-9744-45EE49A5B64C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 29-01-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-02-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Socialfaglige_systemer">'Opdateret d. 29-01-2026'!$A$1:$E$11</definedName>
+    <definedName name="Socialfaglige_systemer">'Opdateret d. 02-02-2026'!$A$1:$E$11</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Socialfaglige systemer_excel.XLSX
+++ b/html/Socialfaglige systemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9673C411-FA17-460A-9744-45EE49A5B64C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CE92A5A-D5D5-4358-B576-7AFFFA69ADFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-02-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 20-02-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Socialfaglige_systemer">'Opdateret d. 02-02-2026'!$A$1:$E$11</definedName>
+    <definedName name="Socialfaglige_systemer">'Opdateret d. 20-02-2026'!$A$1:$E$11</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -428,9 +428,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -447,7 +447,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -464,7 +464,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -481,7 +481,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -498,7 +498,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -515,7 +515,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -532,7 +532,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -549,7 +549,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -566,7 +566,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -583,7 +583,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -600,7 +600,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>18</v>
       </c>

--- a/html/Socialfaglige systemer_excel.XLSX
+++ b/html/Socialfaglige systemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CE92A5A-D5D5-4358-B576-7AFFFA69ADFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BE27C52-BFFF-4708-9D60-10C460A4D701}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 20-02-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 04-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Socialfaglige_systemer">'Opdateret d. 20-02-2026'!$A$1:$E$11</definedName>
+    <definedName name="Socialfaglige_systemer">'Opdateret d. 04-03-2026'!$A$1:$E$11</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Socialfaglige systemer_excel.XLSX
+++ b/html/Socialfaglige systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BE27C52-BFFF-4708-9D60-10C460A4D701}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59E6B013-CA9C-4D79-AC3A-6375E5339EE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 04-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 06-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Socialfaglige_systemer">'Opdateret d. 04-03-2026'!$A$1:$E$11</definedName>
+    <definedName name="Socialfaglige_systemer">'Opdateret d. 06-03-2026'!$A$1:$E$11</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Socialfaglige systemer_excel.XLSX
+++ b/html/Socialfaglige systemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59E6B013-CA9C-4D79-AC3A-6375E5339EE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A985E06B-2D3F-4C46-B556-74A546375E46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Socialfaglige systemer_excel.XLSX
+++ b/html/Socialfaglige systemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A985E06B-2D3F-4C46-B556-74A546375E46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02E16F85-B119-42F4-A076-65CC5C0E2F0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Socialfaglige systemer_excel.XLSX
+++ b/html/Socialfaglige systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02E16F85-B119-42F4-A076-65CC5C0E2F0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{998CF742-61EB-4F0C-A3DC-EF672A46AA91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 06-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Socialfaglige_systemer">'Opdateret d. 06-03-2026'!$A$1:$E$11</definedName>
+    <definedName name="Socialfaglige_systemer">'Opdateret d. 09-03-2026'!$A$1:$E$11</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Socialfaglige systemer_excel.XLSX
+++ b/html/Socialfaglige systemer_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{998CF742-61EB-4F0C-A3DC-EF672A46AA91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DB49F78-8F7A-4C27-9387-C871B0739CA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 09-03-2026" sheetId="1" r:id="rId1"/>

--- a/html/Socialfaglige systemer_excel.XLSX
+++ b/html/Socialfaglige systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DB49F78-8F7A-4C27-9387-C871B0739CA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6381A455-5F62-4568-B690-5B9824E2A757}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 11-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Socialfaglige_systemer">'Opdateret d. 09-03-2026'!$A$1:$E$11</definedName>
+    <definedName name="Socialfaglige_systemer">'Opdateret d. 11-03-2026'!$A$1:$E$11</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Socialfaglige systemer_excel.XLSX
+++ b/html/Socialfaglige systemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6381A455-5F62-4568-B690-5B9824E2A757}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3DC6C2F-CBED-40FF-9FC4-3DFAB75F1D60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Socialfaglige systemer_excel.XLSX
+++ b/html/Socialfaglige systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3DC6C2F-CBED-40FF-9FC4-3DFAB75F1D60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91F882D6-2B20-4800-8E43-2025CA91F08A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 11-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 20-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Socialfaglige_systemer">'Opdateret d. 11-03-2026'!$A$1:$E$11</definedName>
+    <definedName name="Socialfaglige_systemer">'Opdateret d. 20-03-2026'!$A$1:$E$11</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Socialfaglige systemer_excel.XLSX
+++ b/html/Socialfaglige systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91F882D6-2B20-4800-8E43-2025CA91F08A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1220B88B-D58B-449F-871D-1646BED523E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 20-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 25-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Socialfaglige_systemer">'Opdateret d. 20-03-2026'!$A$1:$E$11</definedName>
+    <definedName name="Socialfaglige_systemer">'Opdateret d. 25-03-2026'!$A$1:$E$11</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Socialfaglige systemer_excel.XLSX
+++ b/html/Socialfaglige systemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1220B88B-D58B-449F-871D-1646BED523E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61147FE4-3EBC-4D68-BC26-4CE45AF8F8EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 25-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 08-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Socialfaglige_systemer">'Opdateret d. 25-03-2026'!$A$1:$E$11</definedName>
+    <definedName name="Socialfaglige_systemer">'Opdateret d. 08-04-2026'!$A$1:$E$11</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Socialfaglige systemer_excel.XLSX
+++ b/html/Socialfaglige systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61147FE4-3EBC-4D68-BC26-4CE45AF8F8EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD4CE953-87CA-4053-80B7-A70D2523C563}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 08-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 10-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Socialfaglige_systemer">'Opdateret d. 08-04-2026'!$A$1:$E$11</definedName>
+    <definedName name="Socialfaglige_systemer">'Opdateret d. 10-04-2026'!$A$1:$E$11</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Socialfaglige systemer_excel.XLSX
+++ b/html/Socialfaglige systemer_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD4CE953-87CA-4053-80B7-A70D2523C563}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E3A3369-F342-4DB4-BD05-6515461416F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-15045" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 10-04-2026" sheetId="1" r:id="rId1"/>

--- a/html/Socialfaglige systemer_excel.XLSX
+++ b/html/Socialfaglige systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E3A3369-F342-4DB4-BD05-6515461416F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29993D15-9815-4877-A836-D78EF663400C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-15045" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 10-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 14-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Socialfaglige_systemer">'Opdateret d. 10-04-2026'!$A$1:$E$11</definedName>
+    <definedName name="Socialfaglige_systemer">'Opdateret d. 14-04-2026'!$A$1:$E$11</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Socialfaglige systemer_excel.XLSX
+++ b/html/Socialfaglige systemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29993D15-9815-4877-A836-D78EF663400C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F258D5E-E7F2-4F29-9506-2A960AD82269}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 14-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 24-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Socialfaglige_systemer">'Opdateret d. 14-04-2026'!$A$1:$E$11</definedName>
+    <definedName name="Socialfaglige_systemer">'Opdateret d. 24-04-2026'!$A$1:$E$11</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Socialfaglige systemer_excel.XLSX
+++ b/html/Socialfaglige systemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F258D5E-E7F2-4F29-9506-2A960AD82269}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{320F3845-00FD-41C4-9075-9518ACB359DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Socialfaglige systemer_excel.XLSX
+++ b/html/Socialfaglige systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{320F3845-00FD-41C4-9075-9518ACB359DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38EADA05-BAFB-4683-B948-96D5664240DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 24-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 27-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Socialfaglige_systemer">'Opdateret d. 24-04-2026'!$A$1:$E$11</definedName>
+    <definedName name="Socialfaglige_systemer">'Opdateret d. 27-04-2026'!$A$1:$E$11</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Socialfaglige systemer_excel.XLSX
+++ b/html/Socialfaglige systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38EADA05-BAFB-4683-B948-96D5664240DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCA19624-8111-4C91-880D-86D31698686D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 27-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 06-05-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Socialfaglige_systemer">'Opdateret d. 27-04-2026'!$A$1:$E$11</definedName>
+    <definedName name="Socialfaglige_systemer">'Opdateret d. 06-05-2026'!$A$1:$E$11</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Socialfaglige systemer_excel.XLSX
+++ b/html/Socialfaglige systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCA19624-8111-4C91-880D-86D31698686D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBF72749-F4BF-444C-82CA-B9CE38142B52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 06-05-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 01-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Socialfaglige_systemer">'Opdateret d. 06-05-2026'!$A$1:$E$11</definedName>
+    <definedName name="Socialfaglige_systemer">'Opdateret d. 01-06-2026'!$A$1:$E$11</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Socialfaglige systemer_excel.XLSX
+++ b/html/Socialfaglige systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBF72749-F4BF-444C-82CA-B9CE38142B52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5543BC54-8F24-42F1-8F7E-F4958B0AC7B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 01-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Socialfaglige_systemer">'Opdateret d. 01-06-2026'!$A$1:$E$11</definedName>
+    <definedName name="Socialfaglige_systemer">'Opdateret d. 02-06-2026'!$A$1:$E$11</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Socialfaglige systemer_excel.XLSX
+++ b/html/Socialfaglige systemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5543BC54-8F24-42F1-8F7E-F4958B0AC7B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9C5536C-7F4E-46C4-9D72-4CDD2C4211E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Socialfaglige systemer_excel.XLSX
+++ b/html/Socialfaglige systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9C5536C-7F4E-46C4-9D72-4CDD2C4211E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C59350F-91C8-4571-807C-455034C5888F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 05-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Socialfaglige_systemer">'Opdateret d. 02-06-2026'!$A$1:$E$11</definedName>
+    <definedName name="Socialfaglige_systemer">'Opdateret d. 05-06-2026'!$A$1:$E$11</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Socialfaglige systemer_excel.XLSX
+++ b/html/Socialfaglige systemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5206210E-0928-45E4-A766-688B10649659}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43E63CFA-080E-4231-8A96-BD89C8403CE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Socialfaglige systemer_excel.XLSX
+++ b/html/Socialfaglige systemer_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA8410D0-FFC6-4081-ACE1-4D9507549229}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{071DC4E5-22EB-495B-B747-9521767D648C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3150" yWindow="3135" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 09-06-2026" sheetId="1" r:id="rId1"/>

--- a/html/Socialfaglige systemer_excel.XLSX
+++ b/html/Socialfaglige systemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{071DC4E5-22EB-495B-B747-9521767D648C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{391FBF47-A7E6-4E45-9935-0A87216CDDBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Socialfaglige systemer_excel.XLSX
+++ b/html/Socialfaglige systemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{391FBF47-A7E6-4E45-9935-0A87216CDDBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FAF9AF0-ABCF-47A6-861F-966028A6CA30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 15-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Socialfaglige_systemer">'Opdateret d. 09-06-2026'!$A$1:$E$11</definedName>
+    <definedName name="Socialfaglige_systemer">'Opdateret d. 15-06-2026'!$A$1:$E$11</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -428,9 +428,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -447,7 +447,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -464,7 +464,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -481,7 +481,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -498,7 +498,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -515,7 +515,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -532,7 +532,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -549,7 +549,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -566,7 +566,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -583,7 +583,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -600,7 +600,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>18</v>
       </c>

--- a/html/Socialfaglige systemer_excel.XLSX
+++ b/html/Socialfaglige systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FAF9AF0-ABCF-47A6-861F-966028A6CA30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39B47BF8-0709-436B-9C1D-9A6F893ECEA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 15-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 22-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Socialfaglige_systemer">'Opdateret d. 15-06-2026'!$A$1:$E$11</definedName>
+    <definedName name="Socialfaglige_systemer">'Opdateret d. 22-06-2026'!$A$1:$E$11</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Socialfaglige systemer_excel.XLSX
+++ b/html/Socialfaglige systemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39B47BF8-0709-436B-9C1D-9A6F893ECEA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31D44163-EC01-4FDC-919C-A2CF75177BEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Socialfaglige_systemer">'Opdateret d. 22-06-2026'!$A$1:$E$11</definedName>
+    <definedName name="Socialfaglige_systemer">'Opdateret d. 23-06-2026'!$A$1:$E$11</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -428,9 +428,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -447,7 +447,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -464,7 +464,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -481,7 +481,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -498,7 +498,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -515,7 +515,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -532,7 +532,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -549,7 +549,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -566,7 +566,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -583,7 +583,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -600,7 +600,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>18</v>
       </c>

--- a/html/Socialfaglige systemer_excel.XLSX
+++ b/html/Socialfaglige systemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31D44163-EC01-4FDC-919C-A2CF75177BEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{021294DB-5555-4F0B-894F-F687D4EDFC76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Socialfaglige systemer_excel.XLSX
+++ b/html/Socialfaglige systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39B47BF8-0709-436B-9C1D-9A6F893ECEA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{943CA0AD-F14E-42B3-828A-927ADC83E614}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Socialfaglige_systemer">'Opdateret d. 22-06-2026'!$A$1:$E$11</definedName>
+    <definedName name="Socialfaglige_systemer">'Opdateret d. 23-06-2026'!$A$1:$E$11</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Socialfaglige systemer_excel.XLSX
+++ b/html/Socialfaglige systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{943CA0AD-F14E-42B3-828A-927ADC83E614}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1754C2C6-67FC-41E9-952F-6C65D023C3D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 23-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 25-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Socialfaglige_systemer">'Opdateret d. 23-06-2026'!$A$1:$E$11</definedName>
+    <definedName name="Socialfaglige_systemer">'Opdateret d. 25-06-2026'!$A$1:$E$11</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Socialfaglige systemer_excel.XLSX
+++ b/html/Socialfaglige systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1754C2C6-67FC-41E9-952F-6C65D023C3D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61CB834D-EBD1-49A8-88AD-909147AC78EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 25-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 30-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Socialfaglige_systemer">'Opdateret d. 25-06-2026'!$A$1:$E$11</definedName>
+    <definedName name="Socialfaglige_systemer">'Opdateret d. 30-06-2026'!$A$1:$E$11</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Socialfaglige systemer_excel.XLSX
+++ b/html/Socialfaglige systemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61CB834D-EBD1-49A8-88AD-909147AC78EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB4CBC6F-FA9B-4E27-A834-998AABE3BEC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Socialfaglige systemer_excel.XLSX
+++ b/html/Socialfaglige systemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB4CBC6F-FA9B-4E27-A834-998AABE3BEC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C044FB8E-F74C-4917-A270-52BCF0A3E77D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 30-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 01-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Socialfaglige_systemer">'Opdateret d. 30-06-2026'!$A$1:$E$11</definedName>
+    <definedName name="Socialfaglige_systemer">'Opdateret d. 01-07-2026'!$A$1:$E$11</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -428,9 +428,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -447,7 +447,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -464,7 +464,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -481,7 +481,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -498,7 +498,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -515,7 +515,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -532,7 +532,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -549,7 +549,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -566,7 +566,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -583,7 +583,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -600,7 +600,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>18</v>
       </c>

--- a/html/Socialfaglige systemer_excel.XLSX
+++ b/html/Socialfaglige systemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C044FB8E-F74C-4917-A270-52BCF0A3E77D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8854F36D-7F59-4927-80E1-CA3788A1303E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 01-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Socialfaglige_systemer">'Opdateret d. 01-07-2026'!$A$1:$E$11</definedName>
+    <definedName name="Socialfaglige_systemer">'Opdateret d. 02-07-2026'!$A$1:$E$11</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Socialfaglige systemer_excel.XLSX
+++ b/html/Socialfaglige systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C044FB8E-F74C-4917-A270-52BCF0A3E77D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{628414CF-F9FC-4F7C-84DA-F3843F5BD9B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 01-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 03-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Socialfaglige_systemer">'Opdateret d. 01-07-2026'!$A$1:$E$11</definedName>
+    <definedName name="Socialfaglige_systemer">'Opdateret d. 03-07-2026'!$A$1:$E$11</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -428,9 +428,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -447,7 +447,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -464,7 +464,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -481,7 +481,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -498,7 +498,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -515,7 +515,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -532,7 +532,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -549,7 +549,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -566,7 +566,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -583,7 +583,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -600,7 +600,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>18</v>
       </c>

--- a/html/Socialfaglige systemer_excel.XLSX
+++ b/html/Socialfaglige systemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8854F36D-7F59-4927-80E1-CA3788A1303E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EACD464E-3AEC-4C08-ACFD-70993E7A84BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 03-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Socialfaglige_systemer">'Opdateret d. 02-07-2026'!$A$1:$E$11</definedName>
+    <definedName name="Socialfaglige_systemer">'Opdateret d. 03-07-2026'!$A$1:$E$11</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -428,9 +428,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -447,7 +447,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -464,7 +464,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -481,7 +481,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -498,7 +498,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -515,7 +515,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -532,7 +532,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -549,7 +549,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -566,7 +566,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -583,7 +583,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -600,7 +600,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>18</v>
       </c>

--- a/html/Socialfaglige systemer_excel.XLSX
+++ b/html/Socialfaglige systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EACD464E-3AEC-4C08-ACFD-70993E7A84BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B38D0E1-7D8C-4223-BBFA-45F473051816}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 03-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Socialfaglige_systemer">'Opdateret d. 03-07-2026'!$A$1:$E$11</definedName>
+    <definedName name="Socialfaglige_systemer">'Opdateret d. 09-07-2026'!$A$1:$E$11</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Socialfaglige systemer_excel.XLSX
+++ b/html/Socialfaglige systemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B38D0E1-7D8C-4223-BBFA-45F473051816}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26A4F637-7F94-46A0-81F2-017EE1E4C8BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 19-08-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Socialfaglige_systemer">'Opdateret d. 09-07-2026'!$A$1:$E$11</definedName>
+    <definedName name="Socialfaglige_systemer">'Opdateret d. 19-08-2026'!$A$1:$E$11</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Socialfaglige systemer_excel.XLSX
+++ b/html/Socialfaglige systemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26A4F637-7F94-46A0-81F2-017EE1E4C8BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07EB82F3-25B3-4304-B833-E9D9377BFC74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4560" yWindow="945" windowWidth="21600" windowHeight="12450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 19-08-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 21-08-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Socialfaglige_systemer">'Opdateret d. 19-08-2026'!$A$1:$E$11</definedName>
+    <definedName name="Socialfaglige_systemer">'Opdateret d. 21-08-2026'!$A$1:$E$11</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -428,9 +428,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -447,7 +447,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -464,7 +464,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -481,7 +481,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -498,7 +498,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -515,7 +515,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -532,7 +532,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -549,7 +549,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -566,7 +566,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -583,7 +583,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -600,7 +600,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>18</v>
       </c>

--- a/html/Socialfaglige systemer_excel.XLSX
+++ b/html/Socialfaglige systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07EB82F3-25B3-4304-B833-E9D9377BFC74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEDAA767-0A06-4AE5-BB1D-2BCD6D2DC27B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4560" yWindow="945" windowWidth="21600" windowHeight="12450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 21-08-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 27-08-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Socialfaglige_systemer">'Opdateret d. 21-08-2026'!$A$1:$E$11</definedName>
+    <definedName name="Socialfaglige_systemer">'Opdateret d. 27-08-2026'!$A$1:$E$11</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -428,9 +428,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -447,7 +447,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -464,7 +464,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -481,7 +481,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -498,7 +498,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -515,7 +515,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -532,7 +532,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -549,7 +549,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -566,7 +566,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -583,7 +583,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -600,7 +600,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>18</v>
       </c>

--- a/html/Socialfaglige systemer_excel.XLSX
+++ b/html/Socialfaglige systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEDAA767-0A06-4AE5-BB1D-2BCD6D2DC27B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D2017CE-8D4B-4D92-97FF-4CDFC0111547}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 27-08-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Socialfaglige_systemer">'Opdateret d. 27-08-2026'!$A$1:$E$11</definedName>
+    <definedName name="Socialfaglige_systemer">'Opdateret d. 02-09-2026'!$A$1:$E$11</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Socialfaglige systemer_excel.XLSX
+++ b/html/Socialfaglige systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D2017CE-8D4B-4D92-97FF-4CDFC0111547}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5960C3D-8BE7-4017-93DA-1FBC786F73CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 06-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Socialfaglige_systemer">'Opdateret d. 02-09-2026'!$A$1:$E$11</definedName>
+    <definedName name="Socialfaglige_systemer">'Opdateret d. 06-09-2026'!$A$1:$E$11</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Socialfaglige systemer_excel.XLSX
+++ b/html/Socialfaglige systemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5960C3D-8BE7-4017-93DA-1FBC786F73CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24CCAD07-00EC-4779-B84C-633C4B3A3ECA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Socialfaglige systemer_excel.XLSX
+++ b/html/Socialfaglige systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24CCAD07-00EC-4779-B84C-633C4B3A3ECA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4ACC494-D6A0-4BA3-8F9B-BDF4173BA282}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 06-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 07-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Socialfaglige_systemer">'Opdateret d. 06-09-2026'!$A$1:$E$11</definedName>
+    <definedName name="Socialfaglige_systemer">'Opdateret d. 07-09-2026'!$A$1:$E$11</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Socialfaglige systemer_excel.XLSX
+++ b/html/Socialfaglige systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4ACC494-D6A0-4BA3-8F9B-BDF4173BA282}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F82492E-A84D-4A53-90F4-832B6119364D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 07-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Socialfaglige_systemer">'Opdateret d. 07-09-2026'!$A$1:$E$11</definedName>
+    <definedName name="Socialfaglige_systemer">'Opdateret d. 09-09-2026'!$A$1:$E$11</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Socialfaglige systemer_excel.XLSX
+++ b/html/Socialfaglige systemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F82492E-A84D-4A53-90F4-832B6119364D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7014C7B-D812-43C9-AAAA-86A697976643}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
